--- a/mluca.xlsx
+++ b/mluca.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11207"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mlcardoso\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/845ca001af2900fe/Investimentos/MLUCA Investimentos/2025.11/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8B47D47C-D692-4B70-9373-E291B5BD1B75}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="5" documentId="13_ncr:1_{ACC63371-36E7-4811-B9ED-569CB32EB7D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8B21F02E-40EA-7141-BFFE-5A21C5A6C9DE}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{BFFC41A4-ACB3-413C-BBDC-4C8AF282F8BA}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="28800" windowHeight="15720" xr2:uid="{BFFC41A4-ACB3-413C-BBDC-4C8AF282F8BA}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="22">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="22">
   <si>
     <t>Mês</t>
   </si>
@@ -200,8 +200,8 @@
     </xf>
   </cellXfs>
   <cellStyles count="2">
-    <cellStyle name="Comma" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Vírgula" xfId="1" builtinId="3"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -533,19 +533,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71290061-EDDE-41D8-9868-A15FA4303E50}">
-  <dimension ref="A1:S31"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:S32"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="11.1640625" customWidth="1"/>
     <col min="2" max="2" width="16" customWidth="1"/>
-    <col min="3" max="4" width="11.140625" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" customWidth="1"/>
-    <col min="6" max="9" width="11.140625" customWidth="1"/>
-    <col min="10" max="10" width="14.140625" customWidth="1"/>
-    <col min="11" max="19" width="11.140625" customWidth="1"/>
+    <col min="3" max="4" width="11.1640625" customWidth="1"/>
+    <col min="5" max="5" width="14.5" customWidth="1"/>
+    <col min="6" max="9" width="11.1640625" customWidth="1"/>
+    <col min="10" max="10" width="14.1640625" customWidth="1"/>
+    <col min="11" max="19" width="11.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" ht="39" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:19" ht="29" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -604,7 +604,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="2" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A2" s="8">
         <v>45077</v>
       </c>
@@ -653,7 +653,7 @@
       <c r="R2" s="6"/>
       <c r="S2" s="1"/>
     </row>
-    <row r="3" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A3" s="8">
         <v>45107</v>
       </c>
@@ -702,7 +702,7 @@
       <c r="R3" s="6"/>
       <c r="S3" s="1"/>
     </row>
-    <row r="4" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A4" s="8">
         <v>45138</v>
       </c>
@@ -751,7 +751,7 @@
       <c r="R4" s="6"/>
       <c r="S4" s="1"/>
     </row>
-    <row r="5" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A5" s="8">
         <v>45169</v>
       </c>
@@ -800,7 +800,7 @@
       <c r="R5" s="6"/>
       <c r="S5" s="1"/>
     </row>
-    <row r="6" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A6" s="8">
         <v>45199</v>
       </c>
@@ -849,7 +849,7 @@
       <c r="R6" s="6"/>
       <c r="S6" s="1"/>
     </row>
-    <row r="7" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A7" s="8">
         <v>45230</v>
       </c>
@@ -898,7 +898,7 @@
       <c r="R7" s="6"/>
       <c r="S7" s="1"/>
     </row>
-    <row r="8" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A8" s="8">
         <v>45260</v>
       </c>
@@ -947,7 +947,7 @@
       <c r="R8" s="6"/>
       <c r="S8" s="1"/>
     </row>
-    <row r="9" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A9" s="8">
         <v>45291</v>
       </c>
@@ -996,7 +996,7 @@
       <c r="R9" s="6"/>
       <c r="S9" s="1"/>
     </row>
-    <row r="10" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A10" s="8">
         <v>45322</v>
       </c>
@@ -1045,7 +1045,7 @@
       <c r="R10" s="6"/>
       <c r="S10" s="1"/>
     </row>
-    <row r="11" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A11" s="8">
         <v>45351</v>
       </c>
@@ -1094,7 +1094,7 @@
       <c r="R11" s="6"/>
       <c r="S11" s="1"/>
     </row>
-    <row r="12" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A12" s="8">
         <v>45382</v>
       </c>
@@ -1143,7 +1143,7 @@
       <c r="R12" s="6"/>
       <c r="S12" s="1"/>
     </row>
-    <row r="13" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A13" s="8">
         <v>45412</v>
       </c>
@@ -1192,7 +1192,7 @@
       <c r="R13" s="6"/>
       <c r="S13" s="1"/>
     </row>
-    <row r="14" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A14" s="8">
         <v>45443</v>
       </c>
@@ -1241,7 +1241,7 @@
       <c r="R14" s="6"/>
       <c r="S14" s="1"/>
     </row>
-    <row r="15" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A15" s="8">
         <v>45473</v>
       </c>
@@ -1290,7 +1290,7 @@
       <c r="R15" s="6"/>
       <c r="S15" s="1"/>
     </row>
-    <row r="16" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A16" s="8">
         <v>45504</v>
       </c>
@@ -1349,7 +1349,7 @@
         <v>0.37040000000000001</v>
       </c>
     </row>
-    <row r="17" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A17" s="8">
         <v>45535</v>
       </c>
@@ -1408,7 +1408,7 @@
         <v>0.35189999999999999</v>
       </c>
     </row>
-    <row r="18" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A18" s="8">
         <v>45565</v>
       </c>
@@ -1467,7 +1467,7 @@
         <v>0.3392</v>
       </c>
     </row>
-    <row r="19" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A19" s="8">
         <v>45596</v>
       </c>
@@ -1526,7 +1526,7 @@
         <v>0.34420000000000001</v>
       </c>
     </row>
-    <row r="20" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A20" s="8">
         <v>45626</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>0.35659999999999997</v>
       </c>
     </row>
-    <row r="21" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A21" s="8">
         <v>45657</v>
       </c>
@@ -1644,7 +1644,7 @@
         <v>0.3674</v>
       </c>
     </row>
-    <row r="22" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A22" s="8">
         <v>45688</v>
       </c>
@@ -1703,7 +1703,7 @@
         <v>0.3947</v>
       </c>
     </row>
-    <row r="23" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A23" s="8">
         <v>45716</v>
       </c>
@@ -1762,7 +1762,7 @@
         <v>0.38490000000000002</v>
       </c>
     </row>
-    <row r="24" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A24" s="8">
         <v>45747</v>
       </c>
@@ -1821,7 +1821,7 @@
         <v>0.39639999999999997</v>
       </c>
     </row>
-    <row r="25" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A25" s="8">
         <v>45777</v>
       </c>
@@ -1880,7 +1880,7 @@
         <v>0.37169999999999997</v>
       </c>
     </row>
-    <row r="26" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A26" s="8">
         <v>45808</v>
       </c>
@@ -1939,7 +1939,7 @@
         <v>0.35570000000000002</v>
       </c>
     </row>
-    <row r="27" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A27" s="8">
         <v>45838</v>
       </c>
@@ -1998,7 +1998,7 @@
         <v>0.34499999999999997</v>
       </c>
     </row>
-    <row r="28" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A28" s="8">
         <v>45869</v>
       </c>
@@ -2057,7 +2057,7 @@
         <v>0.3392</v>
       </c>
     </row>
-    <row r="29" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A29" s="8">
         <v>45900</v>
       </c>
@@ -2116,7 +2116,7 @@
         <v>0.35630000000000001</v>
       </c>
     </row>
-    <row r="30" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A30" s="8">
         <v>45930</v>
       </c>
@@ -2175,7 +2175,7 @@
         <v>0.3589</v>
       </c>
     </row>
-    <row r="31" spans="1:19" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:19" x14ac:dyDescent="0.2">
       <c r="A31" s="8">
         <v>45961</v>
       </c>
@@ -2192,22 +2192,22 @@
         <v>149540</v>
       </c>
       <c r="F31" s="4">
-        <v>2.2599999999999999E-2</v>
+        <v>1.9400000000000001E-2</v>
       </c>
       <c r="G31" s="4">
         <v>0.38030000000000003</v>
       </c>
       <c r="H31" s="4">
-        <v>-3.3999999999999998E-3</v>
+        <v>-2.0000000000000001E-4</v>
       </c>
       <c r="I31" s="4">
-        <v>1.2800000000000001E-2</v>
+        <v>1.21E-2</v>
       </c>
       <c r="J31" s="3">
-        <v>132.321</v>
+        <v>132.2296</v>
       </c>
       <c r="K31" s="4">
-        <v>0.32319999999999999</v>
+        <v>0.32229999999999998</v>
       </c>
       <c r="L31" s="1" t="s">
         <v>20</v>
@@ -2232,6 +2232,65 @@
       </c>
       <c r="S31" s="4">
         <v>0.32469999999999999</v>
+      </c>
+    </row>
+    <row r="32" spans="1:19" x14ac:dyDescent="0.2">
+      <c r="A32" s="8">
+        <v>45991</v>
+      </c>
+      <c r="B32" s="5">
+        <v>1.2203999999999999</v>
+      </c>
+      <c r="C32" s="4">
+        <v>2.6100000000000002E-2</v>
+      </c>
+      <c r="D32" s="4">
+        <v>0.22040000000000001</v>
+      </c>
+      <c r="E32" s="3">
+        <v>159273</v>
+      </c>
+      <c r="F32" s="4">
+        <v>6.5100000000000005E-2</v>
+      </c>
+      <c r="G32" s="4">
+        <v>0.47020000000000001</v>
+      </c>
+      <c r="H32" s="4">
+        <v>-3.9E-2</v>
+      </c>
+      <c r="I32" s="4">
+        <v>1.0500000000000001E-2</v>
+      </c>
+      <c r="J32" s="3">
+        <v>133.71039999999999</v>
+      </c>
+      <c r="K32" s="4">
+        <v>0.33710000000000001</v>
+      </c>
+      <c r="L32" s="1" t="s">
+        <v>20</v>
+      </c>
+      <c r="M32" s="4">
+        <v>4.6300000000000001E-2</v>
+      </c>
+      <c r="N32" s="4">
+        <v>0.1603</v>
+      </c>
+      <c r="O32" s="2">
+        <v>9.4</v>
+      </c>
+      <c r="P32" s="2">
+        <v>2</v>
+      </c>
+      <c r="Q32" s="4">
+        <v>6.6199999999999995E-2</v>
+      </c>
+      <c r="R32" s="7">
+        <v>8476.4</v>
+      </c>
+      <c r="S32" s="4">
+        <v>0.32600000000000001</v>
       </c>
     </row>
   </sheetData>
